--- a/Doc/Tradutor_atividades.xlsx
+++ b/Doc/Tradutor_atividades.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas-torezani\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rsgovbr-my.sharepoint.com/personal/fernanda-silva_spgg_rs_gov_br1/Documents/Projetos/PNAD/PNAD_projetos/Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EE3526C-E2E2-4EB8-9C97-6869DC5AD07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{5EE3526C-E2E2-4EB8-9C97-6869DC5AD07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{206547A8-98D2-41DB-A96C-2FF69CA0B202}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03EF82A7-11BD-44BD-9A83-71FB0EC64BEC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03EF82A7-11BD-44BD-9A83-71FB0EC64BEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Tradutor_SCN12" sheetId="1" r:id="rId1"/>
@@ -1715,7 +1715,7 @@
   <dimension ref="A1:D224"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" style="3" customWidth="1"/>
     <col min="2" max="2" width="39.85546875" style="3" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.28515625" style="3" customWidth="1"/>
